--- a/Market_Performance.xlsx
+++ b/Market_Performance.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-16 13:14:22</t>
+          <t>2026-05-16 19:12:27</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-16 13:14:22</t>
+          <t>2026-05-16 19:12:27</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-16 13:14:22</t>
+          <t>2026-05-16 19:12:27</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-16 13:14:22</t>
+          <t>2026-05-16 19:12:28</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-16 13:14:22</t>
+          <t>2026-05-16 19:12:28</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-16 13:14:22</t>
+          <t>2026-05-16 19:12:28</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-05-16 13:14:22</t>
+          <t>2026-05-16 19:12:28</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-05-16 13:14:22</t>
+          <t>2026-05-16 19:12:28</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-05-16 13:14:22</t>
+          <t>2026-05-16 19:12:28</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-05-16 13:14:23</t>
+          <t>2026-05-16 19:12:28</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-05-16 13:14:23</t>
+          <t>2026-05-16 19:12:28</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-16 13:14:23</t>
+          <t>2026-05-16 19:12:28</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-16 13:14:23</t>
+          <t>2026-05-16 19:12:28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-16 13:14:23</t>
+          <t>2026-05-16 19:12:29</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-16 13:14:23</t>
+          <t>2026-05-16 19:12:29</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-16 13:14:23</t>
+          <t>2026-05-16 19:12:29</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-16 13:14:23</t>
+          <t>2026-05-16 19:12:29</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-05-16 13:14:23</t>
+          <t>2026-05-16 19:12:29</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-05-16 13:14:23</t>
+          <t>2026-05-16 19:12:29</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-05-16 13:14:23</t>
+          <t>2026-05-16 19:12:29</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-05-16 13:14:23</t>
+          <t>2026-05-16 19:12:29</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-05-16 13:14:23</t>
+          <t>2026-05-16 19:12:29</t>
         </is>
       </c>
     </row>
